--- a/artfynd/A 53292-2025 artfynd.xlsx
+++ b/artfynd/A 53292-2025 artfynd.xlsx
@@ -675,67 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123037348</v>
+        <v>123034217</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493257</v>
+        <v>493321</v>
       </c>
       <c r="R2" t="n">
-        <v>7009814</v>
+        <v>7009835</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,11 +748,6 @@
           <t>2025-03-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fyndplats i gammal granskog med hyfsat gott om stående död ved.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -798,12 +774,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,67 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123037385</v>
+        <v>123725254</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493280</v>
+        <v>493410</v>
       </c>
       <c r="R3" t="n">
-        <v>7009843</v>
+        <v>7009704</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,17 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +882,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,53 +919,67 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123034217</v>
+        <v>123725484</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493321</v>
+        <v>493356</v>
       </c>
       <c r="R4" t="n">
-        <v>7009835</v>
+        <v>7009680</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,12 +1003,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,26 +1023,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1074,37 +1040,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123035251</v>
+        <v>124499433</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,14 +1073,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1128,13 +1089,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493214</v>
+        <v>493186</v>
       </c>
       <c r="R5" t="n">
-        <v>7009801</v>
+        <v>7009781</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1158,17 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,7 +1148,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,12 +1169,7 @@
         <v>123034670</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,43 +1287,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123733095</v>
+        <v>123035251</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1376,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493278</v>
+        <v>493214</v>
       </c>
       <c r="R7" t="n">
-        <v>7009820</v>
+        <v>7009801</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1406,12 +1366,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,43 +1408,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123733066</v>
+        <v>123037385</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1496,10 +1460,10 @@
         <v>493280</v>
       </c>
       <c r="R8" t="n">
-        <v>7009832</v>
+        <v>7009843</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,12 +1487,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,37 +1529,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123725484</v>
+        <v>123726570</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1598,14 +1562,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1619,13 +1578,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493356</v>
+        <v>493381</v>
       </c>
       <c r="R9" t="n">
-        <v>7009680</v>
+        <v>7009679</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1655,6 +1614,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,40 +1650,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123725949</v>
+        <v>123725700</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1736,13 +1704,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493389</v>
+        <v>493341</v>
       </c>
       <c r="R10" t="n">
-        <v>7009683</v>
+        <v>7009682</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1772,6 +1740,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1803,40 +1776,44 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123725306</v>
+        <v>124498649</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1848,13 +1825,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493390</v>
+        <v>493256</v>
       </c>
       <c r="R11" t="n">
-        <v>7009685</v>
+        <v>7009831</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1878,12 +1855,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,7 +1889,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1915,15 +1907,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123725818</v>
+        <v>123725306</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,21 +1941,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493368</v>
+        <v>493390</v>
       </c>
       <c r="R12" t="n">
-        <v>7009687</v>
+        <v>7009685</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -2032,15 +2014,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123727294</v>
+        <v>123725818</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,21 +2025,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2082,13 +2059,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493367</v>
+        <v>493368</v>
       </c>
       <c r="R13" t="n">
-        <v>7009725</v>
+        <v>7009687</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,47 +2126,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123726570</v>
+        <v>123733066</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2203,13 +2171,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493381</v>
+        <v>493280</v>
       </c>
       <c r="R14" t="n">
-        <v>7009679</v>
+        <v>7009832</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2239,11 +2207,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2275,15 +2238,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123733427</v>
+        <v>123733311</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2291,21 +2249,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2314,24 +2272,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493324</v>
+        <v>493300</v>
       </c>
       <c r="R15" t="n">
-        <v>7009783</v>
+        <v>7009795</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2392,15 +2345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123726856</v>
+        <v>123725949</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2442,13 +2390,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493371</v>
+        <v>493389</v>
       </c>
       <c r="R16" t="n">
-        <v>7009706</v>
+        <v>7009683</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2509,15 +2457,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123733311</v>
+        <v>123726337</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,21 +2468,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2548,19 +2491,24 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brynjelägden, Brynjelägden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493300</v>
+        <v>493412</v>
       </c>
       <c r="R17" t="n">
-        <v>7009795</v>
+        <v>7009647</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2621,15 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123726337</v>
+        <v>123726856</v>
       </c>
       <c r="B18" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2671,13 +2614,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493412</v>
+        <v>493371</v>
       </c>
       <c r="R18" t="n">
-        <v>7009647</v>
+        <v>7009706</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2738,15 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123733352</v>
+        <v>123727294</v>
       </c>
       <c r="B19" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2788,13 +2726,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493302</v>
+        <v>493367</v>
       </c>
       <c r="R19" t="n">
-        <v>7009788</v>
+        <v>7009725</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2855,49 +2793,35 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123725700</v>
+        <v>123733095</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -2914,13 +2838,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493341</v>
+        <v>493278</v>
       </c>
       <c r="R20" t="n">
-        <v>7009682</v>
+        <v>7009820</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2950,11 +2874,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 32 st plantor inom ca 0,5 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2986,15 +2905,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124499433</v>
+        <v>123733352</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3002,36 +2916,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3040,13 +2950,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493186</v>
+        <v>493302</v>
       </c>
       <c r="R21" t="n">
-        <v>7009781</v>
+        <v>7009788</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3070,22 +2980,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,7 +2999,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3117,15 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124499923</v>
+        <v>123733427</v>
       </c>
       <c r="B22" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,7 +3048,12 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3162,10 +3062,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493294</v>
+        <v>493324</v>
       </c>
       <c r="R22" t="n">
-        <v>7009813</v>
+        <v>7009783</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3192,22 +3092,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,7 +3111,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3242,12 +3132,7 @@
         <v>124499041</v>
       </c>
       <c r="B23" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3361,15 +3246,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124500585</v>
+        <v>124499923</v>
       </c>
       <c r="B24" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3406,13 +3286,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>493320</v>
+        <v>493294</v>
       </c>
       <c r="R24" t="n">
-        <v>7009826</v>
+        <v>7009813</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3441,7 +3321,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3451,7 +3331,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3483,52 +3363,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124498649</v>
+        <v>124500585</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3537,13 +3403,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>493256</v>
+        <v>493320</v>
       </c>
       <c r="R25" t="n">
-        <v>7009831</v>
+        <v>7009826</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3572,7 +3438,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3582,12 +3448,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor och 1 vinterståndare inom ca 2 x 1 m2 i gammal barrblandskog.</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 53292-2025 artfynd.xlsx
+++ b/artfynd/A 53292-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123034217</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725254</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124499433</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1284,6 +1309,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123034670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123035251</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1526,6 +1561,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123037385</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1647,6 +1687,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726570</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1773,6 +1818,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725700</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1904,6 +1954,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124498649</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2011,6 +2066,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725306</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2123,6 +2183,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725818</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2235,6 +2300,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733066</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2342,6 +2412,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733311</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2454,6 +2529,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123725949</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2566,6 +2646,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726337</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2678,6 +2763,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726856</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2790,6 +2880,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123727294</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2902,6 +2997,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733095</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3014,6 +3114,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733352</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3126,6 +3231,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123733427</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3243,6 +3353,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124499041</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3360,6 +3475,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124499923</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3477,8 +3597,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124500585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>